--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-12-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60bd48255
-	0x7ff60bd482b0
-	0x7ff60bb2165d
-	0x7ff60bb79a33
-	0x7ff60bb79d3c
-	0x7ff60bbcdf67
-	0x7ff60bbcac97
-	0x7ff60bb6ac29
-	0x7ff60bb6ba93
-	0x7ff60c05fff0
-	0x7ff60c05a930
-	0x7ff60c079096
-	0x7ff60bd65754
-	0x7ff60bd6e6fc
-	0x7ff60bd51974
-	0x7ff60bd51b25
-	0x7ff60bd37852
+	0x7ff6a3718255
+	0x7ff6a37182b0
+	0x7ff6a34f165d
+	0x7ff6a3549a33
+	0x7ff6a3549d3c
+	0x7ff6a359df67
+	0x7ff6a359ac97
+	0x7ff6a353ac29
+	0x7ff6a353ba93
+	0x7ff6a3a2fff0
+	0x7ff6a3a2a930
+	0x7ff6a3a49096
+	0x7ff6a3735754
+	0x7ff6a373e6fc
+	0x7ff6a3721974
+	0x7ff6a3721b25
+	0x7ff6a3707852
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
